--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/24.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/24.xlsx
@@ -426,13 +426,13 @@
         <v>-6.516483219374632</v>
       </c>
       <c r="E2">
-        <v>-27.68246858764234</v>
+        <v>-27.9171839239339</v>
       </c>
       <c r="F2">
-        <v>-5.416137931258794</v>
+        <v>-5.132508246009854</v>
       </c>
       <c r="G2">
-        <v>-17.99944163013437</v>
+        <v>-16.85245454059332</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.667506431979213</v>
       </c>
       <c r="E3">
-        <v>-28.56821998964663</v>
+        <v>-28.88667586728803</v>
       </c>
       <c r="F3">
-        <v>-5.479354789603438</v>
+        <v>-4.710970298808047</v>
       </c>
       <c r="G3">
-        <v>-17.88777673863413</v>
+        <v>-15.7892764121236</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.849748776395977</v>
       </c>
       <c r="E4">
-        <v>-28.75118845345254</v>
+        <v>-27.76787107895299</v>
       </c>
       <c r="F4">
-        <v>-5.417797151166601</v>
+        <v>-4.90406522550282</v>
       </c>
       <c r="G4">
-        <v>-17.69925415393623</v>
+        <v>-17.60162140643496</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.03197973677762</v>
       </c>
       <c r="E5">
-        <v>-29.04591059881974</v>
+        <v>-28.64032235279675</v>
       </c>
       <c r="F5">
-        <v>-5.289695930895477</v>
+        <v>-5.101023657764251</v>
       </c>
       <c r="G5">
-        <v>-17.58794363436441</v>
+        <v>-17.11038972677049</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.196020973312711</v>
       </c>
       <c r="E6">
-        <v>-29.51921990939044</v>
+        <v>-29.54227210632648</v>
       </c>
       <c r="F6">
-        <v>-5.402459928703768</v>
+        <v>-4.411754880875435</v>
       </c>
       <c r="G6">
-        <v>-17.69571863770593</v>
+        <v>-16.54907443581784</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.315605496610516</v>
       </c>
       <c r="E7">
-        <v>-29.98527686883785</v>
+        <v>-30.35953033896476</v>
       </c>
       <c r="F7">
-        <v>-5.419296496165668</v>
+        <v>-4.892110227145618</v>
       </c>
       <c r="G7">
-        <v>-17.76332328610595</v>
+        <v>-16.24825040263717</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.360744167352228</v>
       </c>
       <c r="E8">
-        <v>-30.50104515170446</v>
+        <v>-30.80430120633912</v>
       </c>
       <c r="F8">
-        <v>-5.027071157879325</v>
+        <v>-4.530864172989171</v>
       </c>
       <c r="G8">
-        <v>-17.36436611913619</v>
+        <v>-17.29416274326109</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.301065296500298</v>
       </c>
       <c r="E9">
-        <v>-31.0111618990095</v>
+        <v>-29.61580546726303</v>
       </c>
       <c r="F9">
-        <v>-4.903975761823318</v>
+        <v>-4.345507026203948</v>
       </c>
       <c r="G9">
-        <v>-17.31258188048503</v>
+        <v>-17.68247234627045</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.110145593577711</v>
       </c>
       <c r="E10">
-        <v>-32.06312414675432</v>
+        <v>-31.30159784372844</v>
       </c>
       <c r="F10">
-        <v>-5.058075293031305</v>
+        <v>-4.178920684766161</v>
       </c>
       <c r="G10">
-        <v>-17.38493773770313</v>
+        <v>-18.36299113525617</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.768048510887238</v>
       </c>
       <c r="E11">
-        <v>-32.34589112074127</v>
+        <v>-32.23351024552992</v>
       </c>
       <c r="F11">
-        <v>-5.011439036621095</v>
+        <v>-3.88463819471722</v>
       </c>
       <c r="G11">
-        <v>-16.85995377246743</v>
+        <v>-17.59232570575705</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.271373360789628</v>
       </c>
       <c r="E12">
-        <v>-32.49540321857852</v>
+        <v>-32.68458474872295</v>
       </c>
       <c r="F12">
-        <v>-4.994689447736489</v>
+        <v>-4.014771400227411</v>
       </c>
       <c r="G12">
-        <v>-16.82946630234785</v>
+        <v>-16.99432143593747</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.621789349744975</v>
       </c>
       <c r="E13">
-        <v>-32.78421344112871</v>
+        <v>-33.09273384679728</v>
       </c>
       <c r="F13">
-        <v>-5.059168738003</v>
+        <v>-3.98520199741708</v>
       </c>
       <c r="G13">
-        <v>-16.30386874868054</v>
+        <v>-17.21402218789321</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.847185646542056</v>
       </c>
       <c r="E14">
-        <v>-34.07194615960887</v>
+        <v>-33.57613486169407</v>
       </c>
       <c r="F14">
-        <v>-4.792594309210299</v>
+        <v>-3.363517231820468</v>
       </c>
       <c r="G14">
-        <v>-16.01209104333925</v>
+        <v>-14.73338587673741</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.975767827472643</v>
       </c>
       <c r="E15">
-        <v>-34.52782310948704</v>
+        <v>-34.35485351629006</v>
       </c>
       <c r="F15">
-        <v>-4.677347694295818</v>
+        <v>-3.629589669967072</v>
       </c>
       <c r="G15">
-        <v>-15.18167292863187</v>
+        <v>-15.44825249300739</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.05742284956515</v>
       </c>
       <c r="E16">
-        <v>-35.11683945942772</v>
+        <v>-34.6870850118628</v>
       </c>
       <c r="F16">
-        <v>-4.592006799357205</v>
+        <v>-3.668469094017467</v>
       </c>
       <c r="G16">
-        <v>-15.1398980563478</v>
+        <v>-15.66980221331188</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.136759605371394</v>
       </c>
       <c r="E17">
-        <v>-35.70611846086084</v>
+        <v>-35.55954534265458</v>
       </c>
       <c r="F17">
-        <v>-4.594346937270114</v>
+        <v>-3.560566784496206</v>
       </c>
       <c r="G17">
-        <v>-15.01915074357101</v>
+        <v>-14.93961065174851</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.261206273112237</v>
       </c>
       <c r="E18">
-        <v>-36.36733453614281</v>
+        <v>-37.53600008753931</v>
       </c>
       <c r="F18">
-        <v>-4.530814470945002</v>
+        <v>-3.263074370761417</v>
       </c>
       <c r="G18">
-        <v>-14.32453418615514</v>
+        <v>-14.90126629660484</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.4687382333580184</v>
       </c>
       <c r="E19">
-        <v>-37.36087720495168</v>
+        <v>-36.8608295196027</v>
       </c>
       <c r="F19">
-        <v>-4.366521878845568</v>
+        <v>-3.424102366926418</v>
       </c>
       <c r="G19">
-        <v>-13.81263573249851</v>
+        <v>-13.92967854613468</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.2196475643115664</v>
       </c>
       <c r="E20">
-        <v>-37.73642129017078</v>
+        <v>-36.05177914610333</v>
       </c>
       <c r="F20">
-        <v>-4.175279181663455</v>
+        <v>-2.957656137716642</v>
       </c>
       <c r="G20">
-        <v>-13.94861283514346</v>
+        <v>-13.82883512333749</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.7854401101456808</v>
       </c>
       <c r="E21">
-        <v>-38.52356743489506</v>
+        <v>-38.03792256112747</v>
       </c>
       <c r="F21">
-        <v>-3.89371047451268</v>
+        <v>-2.775840261578387</v>
       </c>
       <c r="G21">
-        <v>-13.50417793735979</v>
+        <v>-14.36826630709942</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.231762610434611</v>
       </c>
       <c r="E22">
-        <v>-39.01778697419617</v>
+        <v>-38.27362963322671</v>
       </c>
       <c r="F22">
-        <v>-3.874853518955352</v>
+        <v>-3.026967295043682</v>
       </c>
       <c r="G22">
-        <v>-13.31202304039559</v>
+        <v>-13.12038001399466</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.55782275003541</v>
       </c>
       <c r="E23">
-        <v>-38.9558102789272</v>
+        <v>-38.60420144307564</v>
       </c>
       <c r="F23">
-        <v>-3.885704303564623</v>
+        <v>-2.222432850790121</v>
       </c>
       <c r="G23">
-        <v>-13.30654668161288</v>
+        <v>-13.40561332293563</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.777523215416388</v>
       </c>
       <c r="E24">
-        <v>-39.79066163308527</v>
+        <v>-39.49135893625931</v>
       </c>
       <c r="F24">
-        <v>-3.738734530592532</v>
+        <v>-2.816394644517242</v>
       </c>
       <c r="G24">
-        <v>-12.76648386270075</v>
+        <v>-12.58397903834288</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.901592459944212</v>
       </c>
       <c r="E25">
-        <v>-39.85640375449162</v>
+        <v>-39.9862735963206</v>
       </c>
       <c r="F25">
-        <v>-3.629688245688005</v>
+        <v>-2.543334098960621</v>
       </c>
       <c r="G25">
-        <v>-12.97944826679495</v>
+        <v>-13.12064907416254</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.944044365531632</v>
       </c>
       <c r="E26">
-        <v>-39.87074090319991</v>
+        <v>-40.52201018532403</v>
       </c>
       <c r="F26">
-        <v>-3.597473037393133</v>
+        <v>-2.556023030836704</v>
       </c>
       <c r="G26">
-        <v>-13.05332168898429</v>
+        <v>-12.62272698373836</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.91868207571126</v>
       </c>
       <c r="E27">
-        <v>-39.73575614997927</v>
+        <v>-39.15238680712616</v>
       </c>
       <c r="F27">
-        <v>-3.508263666683445</v>
+        <v>-2.595450834107752</v>
       </c>
       <c r="G27">
-        <v>-13.32373700136281</v>
+        <v>-12.2750323411918</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.835551558331007</v>
       </c>
       <c r="E28">
-        <v>-39.92037750679798</v>
+        <v>-41.30396217036151</v>
       </c>
       <c r="F28">
-        <v>-3.461373101480576</v>
+        <v>-2.389622243697145</v>
       </c>
       <c r="G28">
-        <v>-13.5367506237804</v>
+        <v>-13.17125535427385</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.706107831529411</v>
       </c>
       <c r="E29">
-        <v>-40.43125956621031</v>
+        <v>-39.83361420904802</v>
       </c>
       <c r="F29">
-        <v>-3.661282178430778</v>
+        <v>-2.17879942621506</v>
       </c>
       <c r="G29">
-        <v>-13.34870053498706</v>
+        <v>-12.62635929600467</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.53916815839609</v>
       </c>
       <c r="E30">
-        <v>-40.37039234707322</v>
+        <v>-40.60386688148668</v>
       </c>
       <c r="F30">
-        <v>-3.711911165722481</v>
+        <v>-2.543590064488086</v>
       </c>
       <c r="G30">
-        <v>-13.12076391691712</v>
+        <v>-12.48868908303504</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.344194938957886</v>
       </c>
       <c r="E31">
-        <v>-39.61959626320851</v>
+        <v>-40.63758137047379</v>
       </c>
       <c r="F31">
-        <v>-3.64597891903146</v>
+        <v>-2.670141409348572</v>
       </c>
       <c r="G31">
-        <v>-13.47456819400736</v>
+        <v>-14.01957581380957</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.130725709243778</v>
       </c>
       <c r="E32">
-        <v>-39.16651338179308</v>
+        <v>-40.50696885890756</v>
       </c>
       <c r="F32">
-        <v>-3.570484827409925</v>
+        <v>-2.762502718025912</v>
       </c>
       <c r="G32">
-        <v>-12.9971471758866</v>
+        <v>-12.01030010455424</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.908716467833131</v>
       </c>
       <c r="E33">
-        <v>-39.12175847317528</v>
+        <v>-40.98894566872893</v>
       </c>
       <c r="F33">
-        <v>-3.385044015517019</v>
+        <v>-2.378097996389398</v>
       </c>
       <c r="G33">
-        <v>-13.64399406922929</v>
+        <v>-12.49045109901246</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.6885029666101669</v>
       </c>
       <c r="E34">
-        <v>-39.17113921799191</v>
+        <v>-38.42733056952105</v>
       </c>
       <c r="F34">
-        <v>-3.51761841976326</v>
+        <v>-3.035265879684927</v>
       </c>
       <c r="G34">
-        <v>-13.35153879163598</v>
+        <v>-13.28932026842579</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.4812850169611382</v>
       </c>
       <c r="E35">
-        <v>-38.72802350786736</v>
+        <v>-38.37132466723119</v>
       </c>
       <c r="F35">
-        <v>-3.399247203005419</v>
+        <v>-2.507638090839185</v>
       </c>
       <c r="G35">
-        <v>-13.59625229553937</v>
+        <v>-13.69178178002104</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.2966536042952281</v>
       </c>
       <c r="E36">
-        <v>-38.49614978901562</v>
+        <v>-37.5555381886454</v>
       </c>
       <c r="F36">
-        <v>-3.336594462862081</v>
+        <v>-2.676729415303037</v>
       </c>
       <c r="G36">
-        <v>-14.08026528777306</v>
+        <v>-13.45200979578618</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.1458076646058585</v>
       </c>
       <c r="E37">
-        <v>-37.57915870906941</v>
+        <v>-38.92763864212547</v>
       </c>
       <c r="F37">
-        <v>-3.297135181629727</v>
+        <v>-2.319901872873122</v>
       </c>
       <c r="G37">
-        <v>-13.9484881487242</v>
+        <v>-13.2285257953724</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.03591175076159474</v>
       </c>
       <c r="E38">
-        <v>-37.95661833879375</v>
+        <v>-37.73486123087514</v>
       </c>
       <c r="F38">
-        <v>-3.165048685783734</v>
+        <v>-2.749480782453904</v>
       </c>
       <c r="G38">
-        <v>-13.57906853823256</v>
+        <v>-13.7001915508779</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.02708453996389302</v>
       </c>
       <c r="E39">
-        <v>-36.90714675175315</v>
+        <v>-36.69624892450494</v>
       </c>
       <c r="F39">
-        <v>-3.437164064133761</v>
+        <v>-2.143921845087589</v>
       </c>
       <c r="G39">
-        <v>-13.59507761822109</v>
+        <v>-13.96998179054934</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.04180844535155039</v>
       </c>
       <c r="E40">
-        <v>-36.33329852550116</v>
+        <v>-37.11497880209818</v>
       </c>
       <c r="F40">
-        <v>-3.32483827268155</v>
+        <v>-2.535264972089951</v>
       </c>
       <c r="G40">
-        <v>-14.24863460965285</v>
+        <v>-13.49361568515994</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.01097694742599237</v>
       </c>
       <c r="E41">
-        <v>-36.08634498820388</v>
+        <v>-36.77579157044966</v>
       </c>
       <c r="F41">
-        <v>-3.218233186513074</v>
+        <v>-2.200212723577427</v>
       </c>
       <c r="G41">
-        <v>-14.06216606965116</v>
+        <v>-13.41995554237196</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.05961755679274088</v>
       </c>
       <c r="E42">
-        <v>-35.71275267528208</v>
+        <v>-35.36613648202398</v>
       </c>
       <c r="F42">
-        <v>-3.13599038566093</v>
+        <v>-2.261303162799085</v>
       </c>
       <c r="G42">
-        <v>-14.73755794995025</v>
+        <v>-13.37121627732797</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.1600478427946024</v>
       </c>
       <c r="E43">
-        <v>-35.00314532675414</v>
+        <v>-36.14491627101908</v>
       </c>
       <c r="F43">
-        <v>-3.397863829442744</v>
+        <v>-2.6180122486904</v>
       </c>
       <c r="G43">
-        <v>-13.96177709603995</v>
+        <v>-14.02077181906799</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.2788805186959847</v>
       </c>
       <c r="E44">
-        <v>-34.283971576885</v>
+        <v>-34.2064508945847</v>
       </c>
       <c r="F44">
-        <v>-3.009403421002124</v>
+        <v>-2.321228917452407</v>
       </c>
       <c r="G44">
-        <v>-14.30735042884833</v>
+        <v>-13.72660866565299</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.4021552236527954</v>
       </c>
       <c r="E45">
-        <v>-34.46177078761116</v>
+        <v>-34.63187838523529</v>
       </c>
       <c r="F45">
-        <v>-3.248090032812176</v>
+        <v>-2.613980584540974</v>
       </c>
       <c r="G45">
-        <v>-14.74285220093641</v>
+        <v>-13.5335711200893</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.5163380288630912</v>
       </c>
       <c r="E46">
-        <v>-33.10010393824476</v>
+        <v>-33.2278295476311</v>
       </c>
       <c r="F46">
-        <v>-3.014714912788874</v>
+        <v>-2.413433664690617</v>
       </c>
       <c r="G46">
-        <v>-14.38393414004577</v>
+        <v>-14.21292015358907</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.6084974043553377</v>
       </c>
       <c r="E47">
-        <v>-32.96526409619237</v>
+        <v>-34.15050386245694</v>
       </c>
       <c r="F47">
-        <v>-3.036135665457867</v>
+        <v>-2.476133621775914</v>
       </c>
       <c r="G47">
-        <v>-14.78153124067914</v>
+        <v>-14.4617237001663</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.6687538767301944</v>
       </c>
       <c r="E48">
-        <v>-32.69799582449667</v>
+        <v>-33.4198232601343</v>
       </c>
       <c r="F48">
-        <v>-3.137138502881211</v>
+        <v>-1.980976178385107</v>
       </c>
       <c r="G48">
-        <v>-15.02724715776894</v>
+        <v>-13.41639213575841</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.690069416820516</v>
       </c>
       <c r="E49">
-        <v>-31.74339123944275</v>
+        <v>-31.57326552792259</v>
       </c>
       <c r="F49">
-        <v>-3.118308055080772</v>
+        <v>-1.631618024826235</v>
       </c>
       <c r="G49">
-        <v>-14.71923888998387</v>
+        <v>-14.35569102547285</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.6694432065759836</v>
       </c>
       <c r="E50">
-        <v>-30.85119129045154</v>
+        <v>-30.41693553972299</v>
       </c>
       <c r="F50">
-        <v>-2.931674394127835</v>
+        <v>-1.998947609188842</v>
       </c>
       <c r="G50">
-        <v>-14.41858876154584</v>
+        <v>-13.92371820717195</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.608066854306641</v>
       </c>
       <c r="E51">
-        <v>-31.06871201093598</v>
+        <v>-32.10470006661874</v>
       </c>
       <c r="F51">
-        <v>-3.113090168810538</v>
+        <v>-2.475475069690689</v>
       </c>
       <c r="G51">
-        <v>-15.13670050593812</v>
+        <v>-14.51858070734836</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.5106473023846678</v>
       </c>
       <c r="E52">
-        <v>-30.79022670912327</v>
+        <v>-29.77876260442905</v>
       </c>
       <c r="F52">
-        <v>-3.004829176203865</v>
+        <v>-1.911423966143852</v>
       </c>
       <c r="G52">
-        <v>-15.40870392955141</v>
+        <v>-14.65662497957576</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.3856600492973367</v>
       </c>
       <c r="E53">
-        <v>-30.20461577163637</v>
+        <v>-30.98690965646142</v>
       </c>
       <c r="F53">
-        <v>-2.953375134978974</v>
+        <v>-2.65264711816885</v>
       </c>
       <c r="G53">
-        <v>-15.15075397787722</v>
+        <v>-15.01537241694531</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.2425849570965752</v>
       </c>
       <c r="E54">
-        <v>-29.48669867330435</v>
+        <v>-29.47991049076685</v>
       </c>
       <c r="F54">
-        <v>-3.023801274830182</v>
+        <v>-1.911200306945096</v>
       </c>
       <c r="G54">
-        <v>-15.38124830815275</v>
+        <v>-13.67301647392258</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.09265387239824971</v>
       </c>
       <c r="E55">
-        <v>-29.34843530490216</v>
+        <v>-29.19994664219065</v>
       </c>
       <c r="F55">
-        <v>-3.11208453078354</v>
+        <v>-2.275003531273986</v>
       </c>
       <c r="G55">
-        <v>-15.61016108963663</v>
+        <v>-14.59369279067639</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.05522567428020098</v>
       </c>
       <c r="E56">
-        <v>-28.69691469247061</v>
+        <v>-29.45270341892877</v>
       </c>
       <c r="F56">
-        <v>-3.028537051271987</v>
+        <v>-2.065318062235944</v>
       </c>
       <c r="G56">
-        <v>-15.47201345893011</v>
+        <v>-14.59875571554261</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.1933408576084067</v>
       </c>
       <c r="E57">
-        <v>-28.80327948996277</v>
+        <v>-28.77547918802968</v>
       </c>
       <c r="F57">
-        <v>-3.12961361339418</v>
+        <v>-2.059575819399738</v>
       </c>
       <c r="G57">
-        <v>-15.702155057888</v>
+        <v>-14.86974196047247</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.3168621208910931</v>
       </c>
       <c r="E58">
-        <v>-27.45117224922657</v>
+        <v>-27.68884467904514</v>
       </c>
       <c r="F58">
-        <v>-3.069200778708012</v>
+        <v>-1.875669143936817</v>
       </c>
       <c r="G58">
-        <v>-15.76776144235832</v>
+        <v>-14.72505977703032</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.4235222027182643</v>
       </c>
       <c r="E59">
-        <v>-27.91906324064708</v>
+        <v>-28.07623751650531</v>
       </c>
       <c r="F59">
-        <v>-3.285453544515448</v>
+        <v>-2.071269882025059</v>
       </c>
       <c r="G59">
-        <v>-15.93419156229648</v>
+        <v>-14.81866646567816</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.5115431537274536</v>
       </c>
       <c r="E60">
-        <v>-27.39956575943515</v>
+        <v>-26.31763633494457</v>
       </c>
       <c r="F60">
-        <v>-3.099816409548079</v>
+        <v>-1.987501228416959</v>
       </c>
       <c r="G60">
-        <v>-15.841267367733</v>
+        <v>-15.07766312702981</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.58233536375616</v>
       </c>
       <c r="E61">
-        <v>-27.1425975018699</v>
+        <v>-27.32565653515596</v>
       </c>
       <c r="F61">
-        <v>-3.342518946526903</v>
+        <v>-2.719830199638098</v>
       </c>
       <c r="G61">
-        <v>-16.13880525752189</v>
+        <v>-15.11376804845916</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.6366150219640702</v>
       </c>
       <c r="E62">
-        <v>-26.71241058503725</v>
+        <v>-27.29382589135605</v>
       </c>
       <c r="F62">
-        <v>-3.448068692624214</v>
+        <v>-2.111562500864629</v>
       </c>
       <c r="G62">
-        <v>-16.23367521647011</v>
+        <v>-15.0581890770745</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.6777643774692267</v>
       </c>
       <c r="E63">
-        <v>-26.99256462952177</v>
+        <v>-26.21478110480836</v>
       </c>
       <c r="F63">
-        <v>-3.404591001120878</v>
+        <v>-2.649819071855692</v>
       </c>
       <c r="G63">
-        <v>-16.12413819715117</v>
+        <v>-15.85706973076329</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.7081527421005942</v>
       </c>
       <c r="E64">
-        <v>-26.08300251118515</v>
+        <v>-26.49225429268034</v>
       </c>
       <c r="F64">
-        <v>-3.364723334758944</v>
+        <v>-2.481769833584562</v>
       </c>
       <c r="G64">
-        <v>-16.90381714227409</v>
+        <v>-15.8530075784727</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.7299911667142832</v>
       </c>
       <c r="E65">
-        <v>-26.06726153553449</v>
+        <v>-25.60949168352111</v>
       </c>
       <c r="F65">
-        <v>-3.49296123565153</v>
+        <v>-2.709418449752311</v>
       </c>
       <c r="G65">
-        <v>-16.3464048643664</v>
+        <v>-15.36249448632975</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.7439248770975455</v>
       </c>
       <c r="E66">
-        <v>-26.1482125368956</v>
+        <v>-25.19225167387639</v>
       </c>
       <c r="F66">
-        <v>-3.661291290472209</v>
+        <v>-2.600551920574192</v>
       </c>
       <c r="G66">
-        <v>-16.57238915560847</v>
+        <v>-16.61934671734569</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.7491331332397644</v>
       </c>
       <c r="E67">
-        <v>-25.99515011543635</v>
+        <v>-24.86518716714641</v>
       </c>
       <c r="F67">
-        <v>-3.808849204300288</v>
+        <v>-3.030910323881008</v>
       </c>
       <c r="G67">
-        <v>-16.43497979975283</v>
+        <v>-15.90462283421354</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.7430550076859205</v>
       </c>
       <c r="E68">
-        <v>-25.39149547326587</v>
+        <v>-25.7987592546717</v>
       </c>
       <c r="F68">
-        <v>-3.797443413531141</v>
+        <v>-2.780249661263488</v>
       </c>
       <c r="G68">
-        <v>-16.69496574940465</v>
+        <v>-16.17436713678315</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.722408165413847</v>
       </c>
       <c r="E69">
-        <v>-24.56102315347321</v>
+        <v>-24.41487571182367</v>
       </c>
       <c r="F69">
-        <v>-3.882204451287795</v>
+        <v>-3.140181924719096</v>
       </c>
       <c r="G69">
-        <v>-16.72290371037254</v>
+        <v>-15.38170275733874</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6818439686945306</v>
       </c>
       <c r="E70">
-        <v>-25.18295018826464</v>
+        <v>-24.98897753262008</v>
       </c>
       <c r="F70">
-        <v>-3.920538809587148</v>
+        <v>-3.247559049306982</v>
       </c>
       <c r="G70">
-        <v>-16.56601374211847</v>
+        <v>-14.461845105364</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.6173788015566989</v>
       </c>
       <c r="E71">
-        <v>-24.8835456007735</v>
+        <v>-24.18474771970187</v>
       </c>
       <c r="F71">
-        <v>-4.030674397626356</v>
+        <v>-3.523615799759528</v>
       </c>
       <c r="G71">
-        <v>-16.71824765697969</v>
+        <v>-15.46612530684169</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.5241497099031888</v>
       </c>
       <c r="E72">
-        <v>-24.93100400837389</v>
+        <v>-23.99123696840611</v>
       </c>
       <c r="F72">
-        <v>-3.955119835184416</v>
+        <v>-3.802055763229929</v>
       </c>
       <c r="G72">
-        <v>-16.42506230758941</v>
+        <v>-15.60358880285307</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.3999082412505179</v>
       </c>
       <c r="E73">
-        <v>-24.74205795887785</v>
+        <v>-24.7791054047346</v>
       </c>
       <c r="F73">
-        <v>-4.240575242189125</v>
+        <v>-3.402182108713538</v>
       </c>
       <c r="G73">
-        <v>-15.99595727693147</v>
+        <v>-14.88052897634915</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.2450881505603031</v>
       </c>
       <c r="E74">
-        <v>-25.23888589920738</v>
+        <v>-24.971216857562</v>
       </c>
       <c r="F74">
-        <v>-4.223880325553105</v>
+        <v>-3.359375394806471</v>
       </c>
       <c r="G74">
-        <v>-16.24309724417806</v>
+        <v>-15.10678889020222</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.06285781433525323</v>
       </c>
       <c r="E75">
-        <v>-25.66144686581112</v>
+        <v>-24.79218363766875</v>
       </c>
       <c r="F75">
-        <v>-4.251331592914477</v>
+        <v>-3.552367603943297</v>
       </c>
       <c r="G75">
-        <v>-16.11745106761303</v>
+        <v>-15.91562805132392</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.1382150981179059</v>
       </c>
       <c r="E76">
-        <v>-25.85391153961111</v>
+        <v>-24.30597949736122</v>
       </c>
       <c r="F76">
-        <v>-4.21591640134259</v>
+        <v>-4.248570644360947</v>
       </c>
       <c r="G76">
-        <v>-15.79708243821352</v>
+        <v>-14.92723224341551</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.3487423519712894</v>
       </c>
       <c r="E77">
-        <v>-25.84146276456403</v>
+        <v>-25.79330244349245</v>
       </c>
       <c r="F77">
-        <v>-4.362471990613281</v>
+        <v>-4.121173536382202</v>
       </c>
       <c r="G77">
-        <v>-15.35516915919829</v>
+        <v>-14.67504247618892</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.5552277396305014</v>
       </c>
       <c r="E78">
-        <v>-26.43712012163696</v>
+        <v>-25.79923927291651</v>
       </c>
       <c r="F78">
-        <v>-4.419534907522528</v>
+        <v>-3.854686914534198</v>
       </c>
       <c r="G78">
-        <v>-15.19161831117854</v>
+        <v>-14.07014928170529</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.7441054534524763</v>
       </c>
       <c r="E79">
-        <v>-26.35933905208121</v>
+        <v>-27.42314552359309</v>
       </c>
       <c r="F79">
-        <v>-4.419145574843212</v>
+        <v>-3.872244990003937</v>
       </c>
       <c r="G79">
-        <v>-15.14725619569485</v>
+        <v>-14.06003655685908</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.9010599739540628</v>
       </c>
       <c r="E80">
-        <v>-27.0561081767974</v>
+        <v>-26.71678961940266</v>
       </c>
       <c r="F80">
-        <v>-4.442693575002594</v>
+        <v>-4.121214954752342</v>
       </c>
       <c r="G80">
-        <v>-15.03927447539509</v>
+        <v>-13.57709652407533</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.012996620269124</v>
       </c>
       <c r="E81">
-        <v>-27.15670369840379</v>
+        <v>-27.14970267758793</v>
       </c>
       <c r="F81">
-        <v>-4.671763669633547</v>
+        <v>-3.979252662730174</v>
       </c>
       <c r="G81">
-        <v>-14.9764325200886</v>
+        <v>-13.67362349991108</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.069670623807042</v>
       </c>
       <c r="E82">
-        <v>-27.27340247358146</v>
+        <v>-26.55214788990579</v>
       </c>
       <c r="F82">
-        <v>-4.52174136278214</v>
+        <v>-4.255046820716033</v>
       </c>
       <c r="G82">
-        <v>-14.31460028788392</v>
+        <v>-12.809441615357</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.063879424534303</v>
       </c>
       <c r="E83">
-        <v>-28.59107519796334</v>
+        <v>-26.91269593344849</v>
       </c>
       <c r="F83">
-        <v>-4.712443964417628</v>
+        <v>-4.04769569101908</v>
       </c>
       <c r="G83">
-        <v>-13.89767187043308</v>
+        <v>-12.81955105898165</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.9923888320128346</v>
       </c>
       <c r="E84">
-        <v>-28.71607919447107</v>
+        <v>-27.70822654779796</v>
       </c>
       <c r="F84">
-        <v>-4.731113708941923</v>
+        <v>-3.769826472689209</v>
       </c>
       <c r="G84">
-        <v>-13.94647019746514</v>
+        <v>-13.26019614586416</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.8574234548878021</v>
       </c>
       <c r="E85">
-        <v>-29.38408345229054</v>
+        <v>-28.38471716590781</v>
       </c>
       <c r="F85">
-        <v>-4.83773370572365</v>
+        <v>-4.653888329448536</v>
       </c>
       <c r="G85">
-        <v>-13.28029690913732</v>
+        <v>-12.93227086321325</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.6634538889351801</v>
       </c>
       <c r="E86">
-        <v>-30.46258708619432</v>
+        <v>-30.63694918514866</v>
       </c>
       <c r="F86">
-        <v>-4.898195414086583</v>
+        <v>-4.367323738491478</v>
       </c>
       <c r="G86">
-        <v>-13.32215545257115</v>
+        <v>-12.57221585905227</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.4211389044357714</v>
       </c>
       <c r="E87">
-        <v>-31.10609003539529</v>
+        <v>-31.89733671333351</v>
       </c>
       <c r="F87">
-        <v>-4.868278925334479</v>
+        <v>-4.408280707988094</v>
       </c>
       <c r="G87">
-        <v>-13.06974748411087</v>
+        <v>-12.34182816847742</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.1410786303438792</v>
       </c>
       <c r="E88">
-        <v>-32.36269628778373</v>
+        <v>-32.49217215237404</v>
       </c>
       <c r="F88">
-        <v>-4.998224091444235</v>
+        <v>-4.385331617460936</v>
       </c>
       <c r="G88">
-        <v>-13.00412633414354</v>
+        <v>-12.09963792395324</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.163135151650191</v>
       </c>
       <c r="E89">
-        <v>-33.5108614373475</v>
+        <v>-33.87504131704436</v>
       </c>
       <c r="F89">
-        <v>-5.066203233987573</v>
+        <v>-4.906339094023505</v>
       </c>
       <c r="G89">
-        <v>-13.16042076068456</v>
+        <v>-11.8933278371816</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.4778532872424483</v>
       </c>
       <c r="E90">
-        <v>-34.4050607076131</v>
+        <v>-35.09901085725952</v>
       </c>
       <c r="F90">
-        <v>-5.073250983850592</v>
+        <v>-4.558809975690014</v>
       </c>
       <c r="G90">
-        <v>-12.85361998243337</v>
+        <v>-12.03507332732805</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.7930258981627275</v>
       </c>
       <c r="E91">
-        <v>-35.29992792779483</v>
+        <v>-36.24792773350856</v>
       </c>
       <c r="F91">
-        <v>-5.234947472509652</v>
+        <v>-4.973588444884977</v>
       </c>
       <c r="G91">
-        <v>-12.45316657843249</v>
+        <v>-11.96587892708248</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.096711481643385</v>
       </c>
       <c r="E92">
-        <v>-36.66361900504266</v>
+        <v>-35.81928049783852</v>
       </c>
       <c r="F92">
-        <v>-5.328907530274394</v>
+        <v>-5.205029327022743</v>
       </c>
       <c r="G92">
-        <v>-12.87841945497965</v>
+        <v>-12.09551342845302</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.384952766582655</v>
       </c>
       <c r="E93">
-        <v>-38.36297642539805</v>
+        <v>-37.33566492591398</v>
       </c>
       <c r="F93">
-        <v>-5.159614912531662</v>
+        <v>-5.599027371551077</v>
       </c>
       <c r="G93">
-        <v>-12.95913750534199</v>
+        <v>-12.27354266660381</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.650863678458955</v>
       </c>
       <c r="E94">
-        <v>-39.87742945930923</v>
+        <v>-39.46223405567898</v>
       </c>
       <c r="F94">
-        <v>-5.436128921790554</v>
+        <v>-5.412308388755652</v>
       </c>
       <c r="G94">
-        <v>-13.01998775916189</v>
+        <v>-11.77075452460698</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.8956720077536</v>
       </c>
       <c r="E95">
-        <v>-41.24424971209636</v>
+        <v>-41.03172163420538</v>
       </c>
       <c r="F95">
-        <v>-5.54158257726914</v>
+        <v>-5.116413067373459</v>
       </c>
       <c r="G95">
-        <v>-13.62839514193569</v>
+        <v>-12.10797878915735</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.118078929148027</v>
       </c>
       <c r="E96">
-        <v>-42.92605250296101</v>
+        <v>-42.3022393587454</v>
       </c>
       <c r="F96">
-        <v>-5.628167680046758</v>
+        <v>-5.963081591203015</v>
       </c>
       <c r="G96">
-        <v>-13.74425179397812</v>
+        <v>-12.2425318416455</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.317936755080371</v>
       </c>
       <c r="E97">
-        <v>-44.27580267297623</v>
+        <v>-44.95627608397582</v>
       </c>
       <c r="F97">
-        <v>-5.699814833449693</v>
+        <v>-5.800632944942212</v>
       </c>
       <c r="G97">
-        <v>-13.80006209148272</v>
+        <v>-12.34513563980934</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.49348276277955</v>
       </c>
       <c r="E98">
-        <v>-45.68370524196094</v>
+        <v>-45.58339048574303</v>
       </c>
       <c r="F98">
-        <v>-5.828162078839449</v>
+        <v>-5.505766455874298</v>
       </c>
       <c r="G98">
-        <v>-13.81529188135088</v>
+        <v>-13.07613602248711</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.639365805596451</v>
       </c>
       <c r="E99">
-        <v>-47.71764217166204</v>
+        <v>-47.75881052886577</v>
       </c>
       <c r="F99">
-        <v>-5.840812905815002</v>
+        <v>-5.940162321902358</v>
       </c>
       <c r="G99">
-        <v>-13.91140378265936</v>
+        <v>-13.09586600772405</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.750280615735857</v>
       </c>
       <c r="E100">
-        <v>-49.66280742539077</v>
+        <v>-48.65233505650423</v>
       </c>
       <c r="F100">
-        <v>-5.92134678471517</v>
+        <v>-5.874269008479269</v>
       </c>
       <c r="G100">
-        <v>-14.67095899595819</v>
+        <v>-13.47988377293366</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.817413912118258</v>
       </c>
       <c r="E101">
-        <v>-51.10530300732008</v>
+        <v>-51.37873906061423</v>
       </c>
       <c r="F101">
-        <v>-5.79024024750669</v>
+        <v>-6.366973241806686</v>
       </c>
       <c r="G101">
-        <v>-14.5357382148827</v>
+        <v>-13.97566650690108</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.831711366847017</v>
       </c>
       <c r="E102">
-        <v>-52.85004819053584</v>
+        <v>-52.27715773653647</v>
       </c>
       <c r="F102">
-        <v>-6.273930600940544</v>
+        <v>-6.063989166375037</v>
       </c>
       <c r="G102">
-        <v>-14.39148915268639</v>
+        <v>-13.59338122667486</v>
       </c>
     </row>
   </sheetData>
